--- a/daily_matches/job_matches_2026-09-15.xlsx
+++ b/daily_matches/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II, Java</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sony Interactive Entertainment</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3610bc487a90461</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62ff1bbfe4e73a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
+          <t>Palantir Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, LLaMA, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
+          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Engineer, Officer</t>
+          <t>AI Architect - Irving</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d204bd8be0a5a12</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee1a2242d96963b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Data Architect - Irving,TX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift, PostgreSQL</t>
+          <t>RAG, Glue, Data Lake, CI/CD, Snowflake, Databricks, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Software Engineer II (Full Stack)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
+          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist - Clinical Machine Learning &amp; Flow Cytometry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Docker, Git, NoSQL, Tableau</t>
+          <t>LangChain, RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc16153ffd80ac29</t>
+          <t>https://www.indeed.com/viewjob?jk=822e13528ba776ea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior Clinical Data Analyst (Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tendo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930887aa7df056</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. DevSecOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Data Lake, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe85eb12d0cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Legacy Applications &amp; Modernization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,234 +776,234 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe6636f3653803</t>
+          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expert Data Scientist (Commercial)</t>
+          <t>Advisory Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, Git, Hadoop, NoSQL, Python, SQL</t>
+          <t>Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f18d0fb192726387</t>
+          <t>https://www.indeed.com/viewjob?jk=e25f3c0fff40851d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Databrick Engineer</t>
+          <t>Full Stack Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TradeWind Services</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e3a08c1c44bf91</t>
+          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Sr Engineer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6135cffbb9d8ed1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MySQL, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>America's Test Kitchen</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245a7582957d4563</t>
+          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Internship, Computer Vision Engineer, Cell Engineering (Winter/Spring 2027)</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd215b58bc6ab571</t>
+          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boot Barn</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd4ee1553bc1d65</t>
+          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Metals DX Engineer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19522a290f558444</t>
+          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer, Product Software</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8566db7265ee1f</t>
+          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer 1</t>
+          <t>Senior DevOps Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Software Engineer, Enterprise Applications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,174 +1186,174 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, AKS, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
+          <t>https://www.indeed.com/viewjob?jk=39995b4f5c566351</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>AI Engineer - (Agentic AI &amp; LLM)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, CI/CD, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
+          <t>https://www.indeed.com/viewjob?jk=84ed4f950f243351</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern- Innovation Group- Software Engineer</t>
+          <t>Recruiting Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e114dabf9f8c69dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f265bb1d3462c631</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer, Search &amp; Intelligence</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0fa075a5a184c2</t>
+          <t>https://www.indeed.com/viewjob?jk=32bd53297a3f780b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Associate - Python AI Developer</t>
+          <t>Senior Software Engineer I, Full Stack</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d7758480c2fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optisources LLC</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Sr Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d28b0fe4ad54ce</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2072df4b6b385</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
+          <t>Manufacturing AI Engineer Co-op</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Promega Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
+          <t>https://www.indeed.com/viewjob?jk=2c78772cf55dd9b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Client Experience - Officer</t>
+          <t>Senior Backend Engineer, Core Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, CI/CD, Git, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b184b1fd916a99</t>
+          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer, Applications &amp; Automation</t>
+          <t>AI Internhip Remote 3 hours</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Digital Dive Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,69 +1501,69 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7f6a290f7695d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e336030ec788a0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Machine Learning Engineer, AI-Native Evaluation &amp; Search</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eebfc8ce15790da</t>
+          <t>https://www.indeed.com/viewjob?jk=131ccdefd8bac9c8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=946622b498453ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=b231d3c2eba798f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineering Intern - Summer 2027</t>
+          <t>Intern - IT Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Snowflake, NoSQL, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8d0550b7f637b</t>
+          <t>https://www.indeed.com/viewjob?jk=c088db4fccc5f4a2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Engineer II (Full Time) - United States</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6336d5eb0c40099a</t>
+          <t>https://www.indeed.com/viewjob?jk=db0f54a5f9ea6957</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Senior Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3980a8bc32ccb049</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbaab1acff0c88</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Developer Platform</t>
+          <t>AI/ML Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e51623f65a6d08</t>
+          <t>https://www.indeed.com/viewjob?jk=3af854e635e29372</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Platform</t>
+          <t>Network Fulfilment Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8307700f2c7f48</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b40006e62b2fd6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot Platform</t>
+          <t>Senior Software Engineer Cloud Microservices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>Anderson Merchandisers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,52 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4edc12fdc6e181</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Kin Insurance</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9903a17366b4f3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3475823e7199aeea</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-15.xlsx
+++ b/daily_matches/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vdrive IT Solutions, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, RAG, Copilot, S3, EC2, Glue, Redshift, BigQuery, Data Lake, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62ff1bbfe4e73a</t>
+          <t>https://www.indeed.com/viewjob?jk=667cfa1dd76c2ddd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Palantir Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Archer Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
+          <t>https://www.indeed.com/viewjob?jk=af675a1bad178e96</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Architect - Irving</t>
+          <t>Sr Software Engineer ( Gen AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Snowflake, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee1a2242d96963b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect - Irving,TX</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, CI/CD, Snowflake, Databricks, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
+          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, Copilot, S3, Apache Airflow, Git, Snowflake, Databricks, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AGILE FUEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822e13528ba776ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c7226137c575620c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Clinical Data Analyst (Healthcare Analytics)</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tendo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930887aa7df056</t>
+          <t>https://www.indeed.com/viewjob?jk=a9719c41b6745919</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
+          <t>https://www.indeed.com/viewjob?jk=edf391fcc01c3ef6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
+          <t>https://www.indeed.com/viewjob?jk=388313669772e213</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Advisory Analytics Engineer</t>
+          <t>Senior Software Engineer - Network Automation Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f3c0fff40851d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf7d907bf404a4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Dallas, TX</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
+          <t>https://www.indeed.com/viewjob?jk=45a1a98f641bfba2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Business Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=6ccb5278826da306</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>AI Engineer in the USA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Andersen Lab</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b35ecb6b298536f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Artificial Intelligence Engineer (Full-time Hybrid, Morrisville, NC Based)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Keras, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
+          <t>https://www.indeed.com/viewjob?jk=fc07ac43b73c2ad8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr Product Software Engineer, Avails Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Terraform, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
+          <t>https://www.indeed.com/viewjob?jk=e93ab7548a80d010</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Applied AI Engineer Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>PressW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
+          <t>https://www.indeed.com/viewjob?jk=d87172402bf38a5f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>AGILE FUEL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Terraform, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
+          <t>https://www.indeed.com/viewjob?jk=acf40ef3a7b7c880</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Senior Business Systems Analyst, AI Enablement</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5da5c7dea2e5d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Software Engineer, Early Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0ea964f8b7c8e1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (hybrid)</t>
+          <t>Data Scientist - Machine Learning Focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, S3, Athena, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc30c2a96073376c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Enterprise Applications</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Qodo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, AKS, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39995b4f5c566351</t>
+          <t>https://www.indeed.com/viewjob?jk=bf02c5e2a301e3ed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer - (Agentic AI &amp; LLM)</t>
+          <t>Software Engineer – Healthcare Revenue Cycle Management</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Legacy Health LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, CI/CD, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,89 +1231,89 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ed4f950f243351</t>
+          <t>https://www.indeed.com/viewjob?jk=8918b63ea1a37f1f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Recruiting Analytics Data Engineer</t>
+          <t>Human Resources Associate Development Program 2027</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, FastAPI, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f265bb1d3462c631</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0278524fd89109</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Search &amp; Intelligence</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32bd53297a3f780b</t>
+          <t>https://www.indeed.com/viewjob?jk=48b172516441981a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Full Stack</t>
+          <t>Site Reliability Engineer/ Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>AGILE FUEL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,476 +1322,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Foot Locker</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Foot Locker</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2072df4b6b385</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Manufacturing AI Engineer Co-op</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Promega Corporation</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Databricks, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c78772cf55dd9b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer, Core Services</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ellipsis Health</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Internhip Remote 3 hours</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Digital Dive Technologies</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e336030ec788a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, AI-Native Evaluation &amp; Search</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Atlassian</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=131ccdefd8bac9c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b231d3c2eba798f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Intern - IT Software Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, NoSQL, Tableau, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c088db4fccc5f4a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Platform Engineer II</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ConstructConnect</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db0f54a5f9ea6957</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AI Senior Developer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbaab1acff0c88</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer - Senior Associate</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3af854e635e29372</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Network Fulfilment Data Scientist</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b40006e62b2fd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Cloud Microservices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Anderson Merchandisers</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3475823e7199aeea</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8e1010798f2748</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-15.xlsx
+++ b/daily_matches/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vdrive IT Solutions, Inc</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, EC2, Glue, Redshift, BigQuery, Data Lake, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667cfa1dd76c2ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Archer Technologies</t>
+          <t>VA Simplified</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, S3</t>
+          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, AWS SageMaker, GCP Vertex AI, Docker, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af675a1bad178e96</t>
+          <t>https://www.indeed.com/viewjob?jk=2607541925dcfb86</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer ( Gen AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Snowflake, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Redshift, BigQuery, Synapse, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
+          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Apache Airflow, Git, Snowflake, Databricks, Kafka, PostgreSQL</t>
+          <t>Machine Learning Engineer, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, EC2, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
+          <t>https://www.indeed.com/viewjob?jk=76b221e75a3ba5aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGILE FUEL</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,46 +657,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
+          <t>RAG, S3, Glue, Data Lake, Apache Airflow, CI/CD, Git, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7226137c575620c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec87e7c5d235465</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BJ's Wholesale Club</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9719c41b6745919</t>
+          <t>https://www.indeed.com/viewjob?jk=5e0754a22ac91db2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf391fcc01c3ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EarnIn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Cortex, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388313669772e213</t>
+          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Network Automation Architect</t>
+          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Quest Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Databricks, MongoDB, NoSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf7d907bf404a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Innovation AI Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45a1a98f641bfba2</t>
+          <t>https://www.indeed.com/viewjob?jk=70ddb3532aa70cb5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Analytics Engineer</t>
+          <t>Innovation AI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccb5278826da306</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b765fd5936901</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer in the USA</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Andersen Lab</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Hadoop, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b35ecb6b298536f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer (Full-time Hybrid, Morrisville, NC Based)</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Keras, Git, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Hadoop, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc07ac43b73c2ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer, Avails Management</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Terraform, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93ab7548a80d010</t>
+          <t>https://www.indeed.com/viewjob?jk=347c1452dba0370f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Applied AI Engineer Intern</t>
+          <t>Software Development Engineer — Mobility Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PressW</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87172402bf38a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=57bfdad1ac1598f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGILE FUEL</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PySpark, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf40ef3a7b7c880</t>
+          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst, AI Enablement</t>
+          <t>Research (Professional) Escobar and Hu Lab</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, R, Scala</t>
+          <t>Generative AI, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, PyTorch, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5da5c7dea2e5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=623bf50503ab1ca8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0ea964f8b7c8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=db2a4a10d5db3ca3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning Focus</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, S3, Athena, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30c2a96073376c</t>
+          <t>https://www.indeed.com/viewjob?jk=b71445293675b991</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qodo</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, EC2, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf02c5e2a301e3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ca46288b741312f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer – Healthcare Revenue Cycle Management</t>
+          <t>Software Engineer Test Infrastructure Development</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Legacy Health LLC</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,112 +1231,812 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8918b63ea1a37f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3ecc407ed4c30c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Human Resources Associate Development Program 2027</t>
+          <t>Senior AI Agentic Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Appzlogic Mobility Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, Prompt Engineering, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0278524fd89109</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d7ece872d407b6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Distinguished Cloud Architect (R-19605)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b172516441981a</t>
+          <t>https://www.indeed.com/viewjob?jk=16ae39fb1db9f690</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer/ Platform Engineer</t>
+          <t>Data Scientist Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AGILE FUEL</t>
+          <t>Summit Utilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb44449d64c33d66</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Summit Utilities</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bc306a8f5d02f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Summit Utilities</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed9fe4119730118</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Halvik</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer, AI Enablement</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Feedzai</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, Git, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=affecd8cb2e2daf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Holt Group</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Las Colinas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=314b3d646a486218</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E T Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, EC2, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af47f1ba41090458</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Engineer - US</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=770d45eebe779881</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Aspire Tech Graduate Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LexisNexis Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e98e3b11a29b7738</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Massachusetts</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f596eccf1cb54f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SCADA Engineer Intern – I - Critical Infrastructure</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5253cf0f3f7cbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SCADA Engineer Intern – I - Critical Infrastructure</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7334cbe799f60bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SCADA Engineer Intern – I - Critical Infrastructure</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D39" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8e1010798f2748</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8564efe6389f2d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61359717e750903e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f50f8f895793118c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - AI/ML</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1e02beabbf9d63b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ece4fa61353aea81</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=815f5959d0f29f2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e13151a0822aa33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Career Accelerator Program - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf2dffe71d86746</t>
         </is>
       </c>
     </row>
